--- a/argus/kship/models/187790_model.xlsx
+++ b/argus/kship/models/187790_model.xlsx
@@ -4324,7 +4324,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 29.5, "op_wape_pct": 91.0, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 230.27, "rev_act": 344.65, "op_pred": 5.17, "op_act": 55.18}, {"q": "2025Q4", "rev_pred": 187.56, "rev_act": 217.83, "op_pred": 4.21, "op_act": 2.58}, {"q": "2026Q1", "rev_pred": 121.73, "rev_act": 110.35, "op_pred": 2.74, "op_act": -8.89}, {"q": "2026Q2", "rev_pred": 140.47, "rev_act": 259.5, "op_pred": 3.16, "op_act": 5.83}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 29.5, "op_wape_pct": 91.0, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 230.27, "rev_act": 344.65, "op_pred": 5.17, "op_act": 55.18}, {"q": "2025Q4", "rev_pred": 187.56, "rev_act": 217.83, "op_pred": 4.21, "op_act": 2.58}, {"q": "2026Q1", "rev_pred": 121.73, "rev_act": 110.35, "op_pred": 2.74, "op_act": -8.89}, {"q": "2026Q2", "rev_pred": 140.47, "rev_act": 259.5, "op_pred": 3.16, "op_act": 5.83}]}</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/187790_model.xlsx
+++ b/argus/kship/models/187790_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4574,7 +4574,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5445,35 +5445,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5564,35 +5564,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5683,35 +5683,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5802,35 +5802,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5921,35 +5921,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6040,35 +6040,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6159,35 +6159,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6278,35 +6278,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6404,7 +6404,7 @@
         <v>3045</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3250</v>
+        <v>3190</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6486,7 +6486,7 @@
         <v>4005</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>3295</v>
+        <v>3300</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6650,7 +6650,7 @@
         <v>3053.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3235</v>
+        <v>3220</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9796,7 +9796,7 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>3250</v>
+        <v>3190</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10188,7 +10188,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.01695606925782262</v>
+        <v>0.01695606925782039</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19488,7 +19488,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33862,7 +33862,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39251,7 +39251,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/187790_model.xlsx
+++ b/argus/kship/models/187790_model.xlsx
@@ -4574,7 +4574,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5445,35 +5445,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5564,35 +5564,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5683,35 +5683,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5802,35 +5802,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5921,35 +5921,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6040,35 +6040,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6159,35 +6159,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6278,35 +6278,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6404,7 +6404,7 @@
         <v>3045</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3190</v>
+        <v>3115</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6650,7 +6650,7 @@
         <v>3053.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3220</v>
+        <v>3203.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9796,11 +9796,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>3190</v>
+        <v>3115</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,170원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,140원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19488,7 +19488,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33862,7 +33862,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39251,7 +39251,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/187790_model.xlsx
+++ b/argus/kship/models/187790_model.xlsx
@@ -4574,7 +4574,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19488,7 +19488,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/187790_model.xlsx
+++ b/argus/kship/models/187790_model.xlsx
@@ -5445,35 +5445,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5564,35 +5564,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5683,35 +5683,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5802,35 +5802,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5921,35 +5921,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6040,35 +6040,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6159,35 +6159,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6278,35 +6278,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6404,7 +6404,7 @@
         <v>3045</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3115</v>
+        <v>3080</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6650,7 +6650,7 @@
         <v>3053.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3203.8</v>
+        <v>3192</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9796,11 +9796,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>3115</v>
+        <v>3080</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,140원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,200원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -33862,7 +33862,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39251,7 +39251,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/187790_model.xlsx
+++ b/argus/kship/models/187790_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1734,79 +1734,19 @@
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="AC41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
     <comment ref="AD41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AF41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AG41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AH41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AI41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AK41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AL41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AM41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AN41" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AD42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="AI42" authorId="0" shapeId="0">
+    <comment ref="AI41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="AN42" authorId="0" shapeId="0">
+    <comment ref="AN41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
@@ -3632,159 +3572,69 @@
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="E34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="G34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="H34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="I34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="J34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="L34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="M34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="N34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="O34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="Q34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="R34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="S34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
     <comment ref="T34" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): 지배NI 186억 − (비영업손익 227억 − 12분기 기준선 -0억) × (1 − 7.8%, 분기 유효세율(법인세 16억 ÷ 세전 206억)) × 지배 비중 0.98(그 분기 지배NI/NI) = -19억 ÷ 유통주식수 — 일회성 여부·세효과는 주석 미확인(모델 추정); 보고 EPS 606.8원</t>
-      </text>
-    </comment>
-    <comment ref="V34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="W34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="X34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="Y34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="AA34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="AB34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
+        <t>조정EPS 산식(모델 추정, 일회성 여부·세효과 주석 미확인): 지배NI − 초과 비영업손익 228억 × (1 − 세율 7.8% [분기 유효세율(법인세 16억 ÷ 세전 206억)]) × 지배 비중 0.9776 [그 분기 지배NI/NI] = -19억 ÷ 유통주식수 · 초과 = 비영업손익 227억 − 12분기 기준선 -0억 · 보고 EPS 607원(EPS 행 불변) · 상수 210.03·0.9776 는 모델 one_offs_detected 값(세전·법인세 셀을 바꿔도 재계산되지 않음)</t>
       </text>
     </comment>
     <comment ref="AC34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AD34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AF34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AG34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AH34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AI34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AK34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AL34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AM34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AN34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AC35" authorId="0" shapeId="0">
@@ -4558,7 +4408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4574,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4462,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식</t>
+          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식, 조정EPS 는 EPS 참조(일회성 의심 분기만 산식 셀)</t>
         </is>
       </c>
     </row>
@@ -4737,50 +4587,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 연결된 가정: 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 세율(MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산)</t>
+          <t>· 조정EPS(일회성 의심 1분기: 2024Q4 보고 607→조정 -63원) — 의심 분기 = 지배NI − (비영업손익 − 12분기 기준선) × (1 − 세율) × 지배 비중 ÷ 유통주식수(subQ 수식+메모, 세후 초과·지배 비중은 모델 상수), 다른 분기 = EPS. 보고 EPS 행·TP 12M fwd EPS(추정 분기만) 는 불변. 일회성 여부·세효과는 주석 미확인(모델 추정)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>· 연결된 가정: 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 세율(MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>· 밸류에이션 — PER 밴드 5.0/17.9/23.2배(hist_quarterly(분기 평균가 ÷ TTM EPS, 5분기, 25/50/75 백분위) · 캡 5~30배 적용(원값 1.9/17.9/23.2)) · COE 9.0% · 12M fwd EPS 가중 0.5(가정). 모델 산출값 구간이며 추천이 아니다</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/187790.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
+          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
+          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/187790.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2024Q4: 비영업손익 227억(영업이익 -21억의 11배, 12분기 중위 4억·기준선 0억) → 지배NI 186억·보고 EPS·FY2024 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS -62.7원(보고 606.8원; 초과 비영업손익 228억 × (1 − 세율 7.8%) × 지배 비중 0.98 = 205억 차감 — 추정, 조정EPS 행) / 금융손익 실적→추정 단절: 최근 4분기 실적 +0/-2/+2/-0(중위 -0억) → 추정 2026Q3 -3억(차 -3억, -2336%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
+        <is>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2024Q4: 비영업손익 227억(영업이익 -21억의 11배, 12분기 중위 4억·기준선 0억) → 지배NI 186억·보고 EPS·FY2024 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS -62.7원(보고 606.8원; 초과 비영업손익 228억 × (1 − 세율 7.8%) × 지배 비중 0.98 = 205억 차감 — 추정, 조정EPS 행) / 금융손익 실적→추정 단절: 최근 4분기 실적 +0/-2/+2/-0(중위 -0억) → 추정 2026Q3 -3억(차 -3억, -2336%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 29.5, "op_wape_pct": 91.0, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 230.27, "rev_act": 344.65, "op_pred": 5.17, "op_act": 55.18}, {"q": "2025Q4", "rev_pred": 187.56, "rev_act": 217.83, "op_pred": 4.21, "op_act": 2.58}, {"q": "2026Q1", "rev_pred": 121.73, "rev_act": 110.35, "op_pred": 2.74, "op_act": -8.89}, {"q": "2026Q2", "rev_pred": 140.47, "rev_act": 259.5, "op_pred": 3.16, "op_act": 5.83}]}</t>
         </is>
@@ -4797,7 +4654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO60"/>
+  <dimension ref="A1:AO59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6948,11 +6805,11 @@
         <v/>
       </c>
       <c r="AC22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AD22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AE22" s="25">
@@ -6960,19 +6817,19 @@
         <v/>
       </c>
       <c r="AF22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AG22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AH22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AI22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AJ22" s="25">
@@ -6980,19 +6837,19 @@
         <v/>
       </c>
       <c r="AK22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AL22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AM22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AN22" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AO22" s="25">
@@ -8198,11 +8055,11 @@
         <v/>
       </c>
       <c r="AC30" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AD30" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AE30" s="25">
@@ -8210,19 +8067,19 @@
         <v/>
       </c>
       <c r="AF30" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AG30" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AH30" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AI30" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AJ30" s="25">
@@ -8230,19 +8087,19 @@
         <v/>
       </c>
       <c r="AK30" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AL30" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AM30" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AN30" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AO30" s="25">
@@ -9475,264 +9332,176 @@
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>drv:조정EPS</t>
+          <t>drv:DPS</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>yoy</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>조정EPS YoY</t>
-        </is>
-      </c>
-      <c r="E41" s="21" t="n"/>
-      <c r="F41" s="22" t="n"/>
-      <c r="G41" s="21" t="n"/>
-      <c r="H41" s="21" t="n"/>
-      <c r="I41" s="21" t="n"/>
-      <c r="J41" s="21">
-        <f>IFERROR(subQ!J34/subQ!E34-1,"")</f>
-        <v/>
-      </c>
-      <c r="K41" s="22" t="n"/>
-      <c r="L41" s="21">
-        <f>IFERROR(subQ!L34/subQ!G34-1,"")</f>
-        <v/>
-      </c>
-      <c r="M41" s="21">
-        <f>IFERROR(subQ!M34/subQ!H34-1,"")</f>
-        <v/>
-      </c>
-      <c r="N41" s="21">
-        <f>IFERROR(subQ!N34/subQ!I34-1,"")</f>
-        <v/>
-      </c>
-      <c r="O41" s="21">
-        <f>IFERROR(subQ!O34/subQ!J34-1,"")</f>
-        <v/>
-      </c>
-      <c r="P41" s="22" t="n"/>
-      <c r="Q41" s="21">
-        <f>IFERROR(subQ!Q34/subQ!L34-1,"")</f>
-        <v/>
-      </c>
-      <c r="R41" s="21">
-        <f>IFERROR(subQ!R34/subQ!M34-1,"")</f>
-        <v/>
-      </c>
-      <c r="S41" s="21">
-        <f>IFERROR(subQ!S34/subQ!N34-1,"")</f>
-        <v/>
-      </c>
-      <c r="T41" s="21">
-        <f>IFERROR(subQ!T34/subQ!O34-1,"")</f>
-        <v/>
-      </c>
-      <c r="U41" s="22" t="n"/>
-      <c r="V41" s="21">
-        <f>IFERROR(subQ!V34/subQ!Q34-1,"")</f>
-        <v/>
-      </c>
-      <c r="W41" s="21">
-        <f>IFERROR(subQ!W34/subQ!R34-1,"")</f>
-        <v/>
-      </c>
-      <c r="X41" s="21">
-        <f>IFERROR(subQ!X34/subQ!S34-1,"")</f>
-        <v/>
-      </c>
-      <c r="Y41" s="21">
-        <f>IFERROR(subQ!Y34/subQ!T34-1,"")</f>
-        <v/>
-      </c>
-      <c r="Z41" s="22" t="n"/>
-      <c r="AA41" s="21">
-        <f>IFERROR(subQ!AA34/subQ!V34-1,"")</f>
-        <v/>
-      </c>
-      <c r="AB41" s="23">
-        <f>IFERROR(subQ!AB34/subQ!W34-1,"")</f>
-        <v/>
-      </c>
-      <c r="AC41" s="24" t="n">
-        <v>-1.080904224</v>
-      </c>
-      <c r="AD41" s="24" t="n">
-        <v>-0.894835096</v>
-      </c>
-      <c r="AE41" s="25" t="n"/>
-      <c r="AF41" s="24" t="n">
-        <v>-0.460273973</v>
-      </c>
-      <c r="AG41" s="24" t="n">
-        <v>-1.96969697</v>
-      </c>
-      <c r="AH41" s="24" t="n">
-        <v>-0.051470588</v>
-      </c>
-      <c r="AI41" s="24" t="n">
-        <v>-0.017751479</v>
-      </c>
-      <c r="AJ41" s="25" t="n"/>
-      <c r="AK41" s="24" t="n">
+          <t>DPS (가정, 원)</t>
+        </is>
+      </c>
+      <c r="E41" s="27">
+        <f>subQ!E36</f>
+        <v/>
+      </c>
+      <c r="F41" s="28">
+        <f>subQ!F36</f>
+        <v/>
+      </c>
+      <c r="G41" s="27">
+        <f>subQ!G36</f>
+        <v/>
+      </c>
+      <c r="H41" s="27">
+        <f>subQ!H36</f>
+        <v/>
+      </c>
+      <c r="I41" s="27">
+        <f>subQ!I36</f>
+        <v/>
+      </c>
+      <c r="J41" s="27">
+        <f>subQ!J36</f>
+        <v/>
+      </c>
+      <c r="K41" s="28">
+        <f>subQ!K36</f>
+        <v/>
+      </c>
+      <c r="L41" s="27">
+        <f>subQ!L36</f>
+        <v/>
+      </c>
+      <c r="M41" s="27">
+        <f>subQ!M36</f>
+        <v/>
+      </c>
+      <c r="N41" s="27">
+        <f>subQ!N36</f>
+        <v/>
+      </c>
+      <c r="O41" s="27">
+        <f>subQ!O36</f>
+        <v/>
+      </c>
+      <c r="P41" s="28">
+        <f>subQ!P36</f>
+        <v/>
+      </c>
+      <c r="Q41" s="27">
+        <f>subQ!Q36</f>
+        <v/>
+      </c>
+      <c r="R41" s="27">
+        <f>subQ!R36</f>
+        <v/>
+      </c>
+      <c r="S41" s="27">
+        <f>subQ!S36</f>
+        <v/>
+      </c>
+      <c r="T41" s="27">
+        <f>subQ!T36</f>
+        <v/>
+      </c>
+      <c r="U41" s="28">
+        <f>subQ!U36</f>
+        <v/>
+      </c>
+      <c r="V41" s="27">
+        <f>subQ!V36</f>
+        <v/>
+      </c>
+      <c r="W41" s="27">
+        <f>subQ!W36</f>
+        <v/>
+      </c>
+      <c r="X41" s="27">
+        <f>subQ!X36</f>
+        <v/>
+      </c>
+      <c r="Y41" s="27">
+        <f>subQ!Y36</f>
+        <v/>
+      </c>
+      <c r="Z41" s="28">
+        <f>subQ!Z36</f>
+        <v/>
+      </c>
+      <c r="AA41" s="27">
+        <f>subQ!AA36</f>
+        <v/>
+      </c>
+      <c r="AB41" s="29">
+        <f>subQ!AB36</f>
+        <v/>
+      </c>
+      <c r="AC41" s="33" t="n"/>
+      <c r="AD41" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="AL41" s="24" t="n">
-        <v>-0.03125</v>
-      </c>
-      <c r="AM41" s="24" t="n">
-        <v>-0.015503876</v>
-      </c>
-      <c r="AN41" s="24" t="n">
-        <v>-0.006024096</v>
-      </c>
-      <c r="AO41" s="25" t="n"/>
+      <c r="AE41" s="31">
+        <f>subQ!AE36</f>
+        <v/>
+      </c>
+      <c r="AF41" s="33" t="n"/>
+      <c r="AG41" s="33" t="n"/>
+      <c r="AH41" s="33" t="n"/>
+      <c r="AI41" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="31">
+        <f>subQ!AJ36</f>
+        <v/>
+      </c>
+      <c r="AK41" s="33" t="n"/>
+      <c r="AL41" s="33" t="n"/>
+      <c r="AM41" s="33" t="n"/>
+      <c r="AN41" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" s="31">
+        <f>subQ!AO36</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>drv:DPS</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>abs</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>DPS (가정, 원)</t>
-        </is>
-      </c>
-      <c r="E42" s="27">
-        <f>subQ!E36</f>
-        <v/>
-      </c>
-      <c r="F42" s="28">
-        <f>subQ!F36</f>
-        <v/>
-      </c>
-      <c r="G42" s="27">
-        <f>subQ!G36</f>
-        <v/>
-      </c>
-      <c r="H42" s="27">
-        <f>subQ!H36</f>
-        <v/>
-      </c>
-      <c r="I42" s="27">
-        <f>subQ!I36</f>
-        <v/>
-      </c>
-      <c r="J42" s="27">
-        <f>subQ!J36</f>
-        <v/>
-      </c>
-      <c r="K42" s="28">
-        <f>subQ!K36</f>
-        <v/>
-      </c>
-      <c r="L42" s="27">
-        <f>subQ!L36</f>
-        <v/>
-      </c>
-      <c r="M42" s="27">
-        <f>subQ!M36</f>
-        <v/>
-      </c>
-      <c r="N42" s="27">
-        <f>subQ!N36</f>
-        <v/>
-      </c>
-      <c r="O42" s="27">
-        <f>subQ!O36</f>
-        <v/>
-      </c>
-      <c r="P42" s="28">
-        <f>subQ!P36</f>
-        <v/>
-      </c>
-      <c r="Q42" s="27">
-        <f>subQ!Q36</f>
-        <v/>
-      </c>
-      <c r="R42" s="27">
-        <f>subQ!R36</f>
-        <v/>
-      </c>
-      <c r="S42" s="27">
-        <f>subQ!S36</f>
-        <v/>
-      </c>
-      <c r="T42" s="27">
-        <f>subQ!T36</f>
-        <v/>
-      </c>
-      <c r="U42" s="28">
-        <f>subQ!U36</f>
-        <v/>
-      </c>
-      <c r="V42" s="27">
-        <f>subQ!V36</f>
-        <v/>
-      </c>
-      <c r="W42" s="27">
-        <f>subQ!W36</f>
-        <v/>
-      </c>
-      <c r="X42" s="27">
-        <f>subQ!X36</f>
-        <v/>
-      </c>
-      <c r="Y42" s="27">
-        <f>subQ!Y36</f>
-        <v/>
-      </c>
-      <c r="Z42" s="28">
-        <f>subQ!Z36</f>
-        <v/>
-      </c>
-      <c r="AA42" s="27">
-        <f>subQ!AA36</f>
-        <v/>
-      </c>
-      <c r="AB42" s="29">
-        <f>subQ!AB36</f>
-        <v/>
-      </c>
-      <c r="AC42" s="33" t="n"/>
-      <c r="AD42" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" s="31">
-        <f>subQ!AE36</f>
-        <v/>
-      </c>
-      <c r="AF42" s="33" t="n"/>
-      <c r="AG42" s="33" t="n"/>
-      <c r="AH42" s="33" t="n"/>
-      <c r="AI42" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" s="31">
-        <f>subQ!AJ36</f>
-        <v/>
-      </c>
-      <c r="AK42" s="33" t="n"/>
-      <c r="AL42" s="33" t="n"/>
-      <c r="AM42" s="33" t="n"/>
-      <c r="AN42" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO42" s="31">
-        <f>subQ!AO36</f>
-        <v/>
-      </c>
+      <c r="F42" s="9" t="n"/>
+      <c r="K42" s="9" t="n"/>
+      <c r="P42" s="9" t="n"/>
+      <c r="U42" s="9" t="n"/>
+      <c r="Z42" s="9" t="n"/>
+      <c r="AB42" s="5" t="n"/>
+      <c r="AC42" s="10" t="n"/>
+      <c r="AD42" s="10" t="n"/>
+      <c r="AE42" s="11" t="n"/>
+      <c r="AF42" s="10" t="n"/>
+      <c r="AG42" s="10" t="n"/>
+      <c r="AH42" s="10" t="n"/>
+      <c r="AI42" s="10" t="n"/>
+      <c r="AJ42" s="11" t="n"/>
+      <c r="AK42" s="10" t="n"/>
+      <c r="AL42" s="10" t="n"/>
+      <c r="AM42" s="10" t="n"/>
+      <c r="AN42" s="10" t="n"/>
+      <c r="AO42" s="11" t="n"/>
     </row>
     <row r="43">
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>3. 밸류에이션·스칼라</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+        </is>
+      </c>
       <c r="F43" s="9" t="n"/>
       <c r="K43" s="9" t="n"/>
       <c r="P43" s="9" t="n"/>
@@ -9754,14 +9523,22 @@
       <c r="AO43" s="11" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>3. 밸류에이션·스칼라</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>sc:종가</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>종가</t>
+        </is>
+      </c>
+      <c r="D44" s="34" t="n">
+        <v>3080</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,200원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9787,20 +9564,22 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>sc:종가</t>
+          <t>sc:기준일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>종가</t>
-        </is>
-      </c>
-      <c r="D45" s="34" t="n">
-        <v>3080</v>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="D45" s="35" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,200원)</t>
+          <t>종가 기준일</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9826,22 +9605,20 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>sc:기준일</t>
+          <t>sc:COE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>기준일</t>
-        </is>
-      </c>
-      <c r="D46" s="35" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
+          <t>COE</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="n">
+        <v>0.09</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>종가 기준일</t>
+          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -9867,20 +9644,20 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>sc:COE</t>
+          <t>sc:PER_lo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>COE</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="n">
-        <v>0.09</v>
+          <t>PER_lo</t>
+        </is>
+      </c>
+      <c r="D47" s="30" t="n">
+        <v>5</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
+          <t>PER 밴드 하단(배) — hist_quarterly(분기 평균가 ÷ TTM EPS, 5분기, 25/50/75 백분위) · 캡 5~30배 적용(원값 1.9/17.9/23.2)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -9906,20 +9683,20 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_lo</t>
+          <t>sc:PER_mid</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PER_lo</t>
+          <t>PER_mid</t>
         </is>
       </c>
       <c r="D48" s="30" t="n">
-        <v>5</v>
+        <v>17.9</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 하단(배) — hist_quarterly(분기 평균가 ÷ TTM EPS, 5분기, 25/50/75 백분위) · 캡 5~30배 적용(원값 1.9/17.9/23.2)</t>
+          <t>PER 밴드 중단(배)</t>
         </is>
       </c>
       <c r="F48" s="9" t="n"/>
@@ -9945,20 +9722,20 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_mid</t>
+          <t>sc:PER_hi</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PER_mid</t>
+          <t>PER_hi</t>
         </is>
       </c>
       <c r="D49" s="30" t="n">
-        <v>17.9</v>
+        <v>23.2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 중단(배)</t>
+          <t>PER 밴드 상단(배)</t>
         </is>
       </c>
       <c r="F49" s="9" t="n"/>
@@ -9984,20 +9761,20 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_hi</t>
+          <t>sc:EPS_Y1가중</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PER_hi</t>
-        </is>
-      </c>
-      <c r="D50" s="30" t="n">
-        <v>23.2</v>
+          <t>EPS_Y1가중</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="n">
+        <v>0.5</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 상단(배)</t>
+          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
         </is>
       </c>
       <c r="F50" s="9" t="n"/>
@@ -10023,20 +9800,20 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>sc:EPS_Y1가중</t>
+          <t>sc:세율</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EPS_Y1가중</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="n">
-        <v>0.5</v>
+          <t>세율</t>
+        </is>
+      </c>
+      <c r="D51" s="36" t="n">
+        <v>0.22</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
+          <t>참고(연결 안 됨: MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산) — 모델 assumptions 값 · 최근 12분기 유효세율 -19.7% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -46.3% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
         </is>
       </c>
       <c r="F51" s="9" t="n"/>
@@ -10062,20 +9839,20 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>sc:세율</t>
+          <t>sc:판관비율</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>세율</t>
+          <t>판관비율</t>
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.22</v>
+        <v>0.1267225613080717</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>참고(연결 안 됨: MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산) — 모델 assumptions 값 · 최근 12분기 유효세율 -19.7% 가 5~27% 밖; 세전 &gt; 0 분기 중위 -46.3% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.1267)</t>
         </is>
       </c>
       <c r="F52" s="9" t="n"/>
@@ -10101,20 +9878,20 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>sc:판관비율</t>
+          <t>sc:지배주주비중</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>판관비율</t>
+          <t>지배주주비중</t>
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.1267225613080717</v>
+        <v>1</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.1267)</t>
+          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
         </is>
       </c>
       <c r="F53" s="9" t="n"/>
@@ -10140,20 +9917,20 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>sc:지배주주비중</t>
+          <t>sc:이자율_자산</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>지배주주비중</t>
+          <t>이자율_자산</t>
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>1</v>
+        <v>0.01695606925782262</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
+          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0171)</t>
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
@@ -10179,20 +9956,20 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_자산</t>
+          <t>sc:이자율_부채</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>이자율_자산</t>
+          <t>이자율_부채</t>
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.01695606925782039</v>
+        <v>0.03522318503544594</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0171)</t>
+          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0353)</t>
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
@@ -10218,20 +9995,20 @@
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_부채</t>
+          <t>sc:배당성향</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>이자율_부채</t>
-        </is>
-      </c>
-      <c r="D56" s="36" t="n">
-        <v>0.03522318503544594</v>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0353)</t>
+          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
         </is>
       </c>
       <c r="F56" s="9" t="n"/>
@@ -10257,20 +10034,18 @@
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>sc:배당성향</t>
+          <t>sc:외화순노출_백만$</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>배당성향</t>
-        </is>
-      </c>
-      <c r="D57" s="24" t="n">
-        <v>0</v>
-      </c>
+          <t>외화순노출_백만$</t>
+        </is>
+      </c>
+      <c r="D57" s="30" t="n"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
+          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
         </is>
       </c>
       <c r="F57" s="9" t="n"/>
@@ -10296,18 +10071,18 @@
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>sc:외화순노출_백만$</t>
+          <t>sc:헤지비율</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>외화순노출_백만$</t>
-        </is>
-      </c>
-      <c r="D58" s="30" t="n"/>
+          <t>헤지비율</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="n"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
+          <t>sls 없음</t>
         </is>
       </c>
       <c r="F58" s="9" t="n"/>
@@ -10333,15 +10108,15 @@
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>sc:헤지비율</t>
+          <t>sc:헤지환율_약정</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>헤지비율</t>
-        </is>
-      </c>
-      <c r="D59" s="24" t="n"/>
+          <t>헤지환율_약정</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="n"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
           <t>sls 없음</t>
@@ -10366,43 +10141,6 @@
       <c r="AM59" s="10" t="n"/>
       <c r="AN59" s="10" t="n"/>
       <c r="AO59" s="11" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t>sc:헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="D60" s="16" t="n"/>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>sls 없음</t>
-        </is>
-      </c>
-      <c r="F60" s="9" t="n"/>
-      <c r="K60" s="9" t="n"/>
-      <c r="P60" s="9" t="n"/>
-      <c r="U60" s="9" t="n"/>
-      <c r="Z60" s="9" t="n"/>
-      <c r="AB60" s="5" t="n"/>
-      <c r="AC60" s="10" t="n"/>
-      <c r="AD60" s="10" t="n"/>
-      <c r="AE60" s="11" t="n"/>
-      <c r="AF60" s="10" t="n"/>
-      <c r="AG60" s="10" t="n"/>
-      <c r="AH60" s="10" t="n"/>
-      <c r="AI60" s="10" t="n"/>
-      <c r="AJ60" s="11" t="n"/>
-      <c r="AK60" s="10" t="n"/>
-      <c r="AL60" s="10" t="n"/>
-      <c r="AM60" s="10" t="n"/>
-      <c r="AN60" s="10" t="n"/>
-      <c r="AO60" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10664,7 +10402,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14774,10 +14512,10 @@
         <v>21484.98</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>19469.41</v>
+        <v>15749.41</v>
       </c>
       <c r="K47" s="37" t="n">
-        <v>19469.41</v>
+        <v>15749.41</v>
       </c>
       <c r="L47" s="18" t="n">
         <v>17402.67</v>
@@ -14869,10 +14607,10 @@
         <v>7205.77</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>2461.86</v>
+        <v>-1258.14</v>
       </c>
       <c r="K48" s="37" t="n">
-        <v>2461.86</v>
+        <v>-1258.14</v>
       </c>
       <c r="L48" s="18" t="n">
         <v>3122.81</v>
@@ -15058,12 +14796,7 @@
       <c r="I50" s="18" t="n">
         <v>4212.92</v>
       </c>
-      <c r="J50" s="18" t="n">
-        <v>3720</v>
-      </c>
-      <c r="K50" s="37" t="n">
-        <v>3720</v>
-      </c>
+      <c r="K50" s="9" t="n"/>
       <c r="L50" s="18" t="n">
         <v>1380.97</v>
       </c>
@@ -19488,7 +19221,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28836,11 +28569,11 @@
         <v/>
       </c>
       <c r="AC12" s="20">
-        <f>IFERROR((AB28*변수!$D$55-AB26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AB28*변수!$D$54-AB26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AD12" s="20">
-        <f>IFERROR((AC28*변수!$D$55-AC26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AC28*변수!$D$54-AC26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AE12" s="38">
@@ -28848,19 +28581,19 @@
         <v/>
       </c>
       <c r="AF12" s="20">
-        <f>IFERROR((AD28*변수!$D$55-AD26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AD28*변수!$D$54-AD26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AG12" s="20">
-        <f>IFERROR((AF28*변수!$D$55-AF26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AF28*변수!$D$54-AF26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AH12" s="20">
-        <f>IFERROR((AG28*변수!$D$55-AG26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AG28*변수!$D$54-AG26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AI12" s="20">
-        <f>IFERROR((AH28*변수!$D$55-AH26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AH28*변수!$D$54-AH26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AJ12" s="38">
@@ -28868,19 +28601,19 @@
         <v/>
       </c>
       <c r="AK12" s="20">
-        <f>IFERROR((AI28*변수!$D$55-AI26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AI28*변수!$D$54-AI26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AL12" s="20">
-        <f>IFERROR((AK28*변수!$D$55-AK26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AK28*변수!$D$54-AK26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AM12" s="20">
-        <f>IFERROR((AL28*변수!$D$55-AL26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AL28*변수!$D$54-AL26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AN12" s="20">
-        <f>IFERROR((AM28*변수!$D$55-AM26*변수!$D$56)/4,"")</f>
+        <f>IFERROR((AM28*변수!$D$54-AM26*변수!$D$55)/4,"")</f>
         <v/>
       </c>
       <c r="AO12" s="38">
@@ -32166,86 +31899,105 @@
           <t>조정 EPS(일회성 의심 분기의 초과 비영업손익 세후 차감 — 모델 추정)</t>
         </is>
       </c>
-      <c r="E34" s="18" t="n">
-        <v>-181.7</v>
+      <c r="E34" s="18">
+        <f>IFERROR(E33,"")</f>
+        <v/>
       </c>
       <c r="F34" s="37" t="n"/>
-      <c r="G34" s="18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H34" s="18" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="I34" s="18" t="n">
-        <v>-30.9</v>
-      </c>
-      <c r="J34" s="18" t="n">
-        <v>-545.4</v>
+      <c r="G34" s="18">
+        <f>IFERROR(G33,"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="18">
+        <f>IFERROR(H33,"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="18">
+        <f>IFERROR(I33,"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="18">
+        <f>IFERROR(J33,"")</f>
+        <v/>
       </c>
       <c r="K34" s="37">
         <f>SUM(G34:J34)</f>
         <v/>
       </c>
-      <c r="L34" s="18" t="n">
-        <v>-73.5</v>
-      </c>
-      <c r="M34" s="18" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="N34" s="18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O34" s="18" t="n">
-        <v>-182</v>
+      <c r="L34" s="18">
+        <f>IFERROR(L33,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="18">
+        <f>IFERROR(M33,"")</f>
+        <v/>
+      </c>
+      <c r="N34" s="18">
+        <f>IFERROR(N33,"")</f>
+        <v/>
+      </c>
+      <c r="O34" s="18">
+        <f>IFERROR(O33,"")</f>
+        <v/>
       </c>
       <c r="P34" s="37">
         <f>SUM(L34:O34)</f>
         <v/>
       </c>
-      <c r="Q34" s="18" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="R34" s="18" t="n">
-        <v>203.1</v>
-      </c>
-      <c r="S34" s="18" t="n">
-        <v>131.7</v>
-      </c>
-      <c r="T34" s="20" t="n">
-        <v>-62.7</v>
+      <c r="Q34" s="18">
+        <f>IFERROR(Q33,"")</f>
+        <v/>
+      </c>
+      <c r="R34" s="18">
+        <f>IFERROR(R33,"")</f>
+        <v/>
+      </c>
+      <c r="S34" s="18">
+        <f>IFERROR(S33,"")</f>
+        <v/>
+      </c>
+      <c r="T34" s="20">
+        <f>IFERROR((T21-(210.03)*(0.9776))*100/T32,"")</f>
+        <v/>
       </c>
       <c r="U34" s="37">
         <f>SUM(Q34:T34)</f>
         <v/>
       </c>
-      <c r="V34" s="18" t="n">
-        <v>110.2</v>
-      </c>
-      <c r="W34" s="18" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="X34" s="18" t="n">
-        <v>168.1</v>
-      </c>
-      <c r="Y34" s="18" t="n">
-        <v>-160.7</v>
+      <c r="V34" s="18">
+        <f>IFERROR(V33,"")</f>
+        <v/>
+      </c>
+      <c r="W34" s="18">
+        <f>IFERROR(W33,"")</f>
+        <v/>
+      </c>
+      <c r="X34" s="18">
+        <f>IFERROR(X33,"")</f>
+        <v/>
+      </c>
+      <c r="Y34" s="18">
+        <f>IFERROR(Y33,"")</f>
+        <v/>
       </c>
       <c r="Z34" s="37">
         <f>SUM(V34:Y34)</f>
         <v/>
       </c>
-      <c r="AA34" s="18" t="n">
-        <v>-36.5</v>
-      </c>
-      <c r="AB34" s="19" t="n">
-        <v>16.5</v>
+      <c r="AA34" s="18">
+        <f>IFERROR(AA33,"")</f>
+        <v/>
+      </c>
+      <c r="AB34" s="19">
+        <f>IFERROR(AB33,"")</f>
+        <v/>
       </c>
       <c r="AC34" s="20">
-        <f>IFERROR(X34*(1+변수!AC41),"")</f>
+        <f>IFERROR(AC33,"")</f>
         <v/>
       </c>
       <c r="AD34" s="20">
-        <f>IFERROR(Y34*(1+변수!AD41),"")</f>
+        <f>IFERROR(AD33,"")</f>
         <v/>
       </c>
       <c r="AE34" s="38">
@@ -32253,19 +32005,19 @@
         <v/>
       </c>
       <c r="AF34" s="20">
-        <f>IFERROR(AA34*(1+변수!AF41),"")</f>
+        <f>IFERROR(AF33,"")</f>
         <v/>
       </c>
       <c r="AG34" s="20">
-        <f>IFERROR(AB34*(1+변수!AG41),"")</f>
+        <f>IFERROR(AG33,"")</f>
         <v/>
       </c>
       <c r="AH34" s="20">
-        <f>IFERROR(AC34*(1+변수!AH41),"")</f>
+        <f>IFERROR(AH33,"")</f>
         <v/>
       </c>
       <c r="AI34" s="20">
-        <f>IFERROR(AD34*(1+변수!AI41),"")</f>
+        <f>IFERROR(AI33,"")</f>
         <v/>
       </c>
       <c r="AJ34" s="38">
@@ -32273,19 +32025,19 @@
         <v/>
       </c>
       <c r="AK34" s="20">
-        <f>IFERROR(AF34*(1+변수!AK41),"")</f>
+        <f>IFERROR(AK33,"")</f>
         <v/>
       </c>
       <c r="AL34" s="20">
-        <f>IFERROR(AG34*(1+변수!AL41),"")</f>
+        <f>IFERROR(AL33,"")</f>
         <v/>
       </c>
       <c r="AM34" s="20">
-        <f>IFERROR(AH34*(1+변수!AM41),"")</f>
+        <f>IFERROR(AM33,"")</f>
         <v/>
       </c>
       <c r="AN34" s="20">
-        <f>IFERROR(AI34*(1+변수!AN41),"")</f>
+        <f>IFERROR(AN33,"")</f>
         <v/>
       </c>
       <c r="AO34" s="38">
@@ -32534,7 +32286,7 @@
       <c r="AB36" s="19" t="n"/>
       <c r="AC36" s="20" t="n"/>
       <c r="AD36" s="20">
-        <f>변수!AD42</f>
+        <f>변수!AD41</f>
         <v/>
       </c>
       <c r="AE36" s="38">
@@ -32545,7 +32297,7 @@
       <c r="AG36" s="20" t="n"/>
       <c r="AH36" s="20" t="n"/>
       <c r="AI36" s="20">
-        <f>변수!AI42</f>
+        <f>변수!AI41</f>
         <v/>
       </c>
       <c r="AJ36" s="38">
@@ -32556,7 +32308,7 @@
       <c r="AL36" s="20" t="n"/>
       <c r="AM36" s="20" t="n"/>
       <c r="AN36" s="20">
-        <f>변수!AN42</f>
+        <f>변수!AN41</f>
         <v/>
       </c>
       <c r="AO36" s="38">
@@ -32771,11 +32523,11 @@
         <v/>
       </c>
       <c r="AC38" s="39">
-        <f>IFERROR(변수!$D$45/AC35,"")</f>
+        <f>IFERROR(변수!$D$44/AC35,"")</f>
         <v/>
       </c>
       <c r="AD38" s="39">
-        <f>IFERROR(변수!$D$45/AD35,"")</f>
+        <f>IFERROR(변수!$D$44/AD35,"")</f>
         <v/>
       </c>
       <c r="AE38" s="40">
@@ -32783,19 +32535,19 @@
         <v/>
       </c>
       <c r="AF38" s="39">
-        <f>IFERROR(변수!$D$45/AF35,"")</f>
+        <f>IFERROR(변수!$D$44/AF35,"")</f>
         <v/>
       </c>
       <c r="AG38" s="39">
-        <f>IFERROR(변수!$D$45/AG35,"")</f>
+        <f>IFERROR(변수!$D$44/AG35,"")</f>
         <v/>
       </c>
       <c r="AH38" s="39">
-        <f>IFERROR(변수!$D$45/AH35,"")</f>
+        <f>IFERROR(변수!$D$44/AH35,"")</f>
         <v/>
       </c>
       <c r="AI38" s="39">
-        <f>IFERROR(변수!$D$45/AI35,"")</f>
+        <f>IFERROR(변수!$D$44/AI35,"")</f>
         <v/>
       </c>
       <c r="AJ38" s="40">
@@ -32803,19 +32555,19 @@
         <v/>
       </c>
       <c r="AK38" s="39">
-        <f>IFERROR(변수!$D$45/AK35,"")</f>
+        <f>IFERROR(변수!$D$44/AK35,"")</f>
         <v/>
       </c>
       <c r="AL38" s="39">
-        <f>IFERROR(변수!$D$45/AL35,"")</f>
+        <f>IFERROR(변수!$D$44/AL35,"")</f>
         <v/>
       </c>
       <c r="AM38" s="39">
-        <f>IFERROR(변수!$D$45/AM35,"")</f>
+        <f>IFERROR(변수!$D$44/AM35,"")</f>
         <v/>
       </c>
       <c r="AN38" s="39">
-        <f>IFERROR(변수!$D$45/AN35,"")</f>
+        <f>IFERROR(변수!$D$44/AN35,"")</f>
         <v/>
       </c>
       <c r="AO38" s="40">
@@ -33849,7 +33601,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D45</f>
+        <f>변수!D44</f>
         <v/>
       </c>
       <c r="W2" s="42" t="n"/>
@@ -39238,7 +38990,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D45</f>
+        <f>변수!D44</f>
         <v/>
       </c>
       <c r="I2" s="42" t="n"/>
@@ -41093,7 +40845,7 @@
         </is>
       </c>
       <c r="C1" s="18">
-        <f>변수!D45</f>
+        <f>변수!D44</f>
         <v/>
       </c>
     </row>
@@ -41104,7 +40856,7 @@
         </is>
       </c>
       <c r="C2">
-        <f>변수!D46</f>
+        <f>변수!D45</f>
         <v/>
       </c>
     </row>
@@ -41281,7 +41033,7 @@
         </is>
       </c>
       <c r="D14" s="18">
-        <f>IFERROR(E7*변수!D51+F7*(1-변수!D51),"")</f>
+        <f>IFERROR(E7*변수!D50+F7*(1-변수!D50),"")</f>
         <v/>
       </c>
     </row>
@@ -41292,7 +41044,7 @@
         </is>
       </c>
       <c r="D15" s="27">
-        <f>변수!D48</f>
+        <f>변수!D47</f>
         <v/>
       </c>
       <c r="E15" s="18">
@@ -41316,7 +41068,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D49</f>
+        <f>변수!D48</f>
         <v/>
       </c>
       <c r="E16" s="18">
@@ -41340,7 +41092,7 @@
         </is>
       </c>
       <c r="D17" s="27">
-        <f>변수!D50</f>
+        <f>변수!D49</f>
         <v/>
       </c>
       <c r="E17" s="18">
@@ -41404,7 +41156,7 @@
         </is>
       </c>
       <c r="D23" s="21">
-        <f>변수!D47</f>
+        <f>변수!D46</f>
         <v/>
       </c>
     </row>
@@ -43203,7 +42955,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D58</f>
+        <f>변수!D57</f>
         <v/>
       </c>
       <c r="E16" s="2" t="inlineStr">

--- a/argus/kship/models/187790_model.xlsx
+++ b/argus/kship/models/187790_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -5302,35 +5302,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5421,35 +5421,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5540,35 +5540,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5659,35 +5659,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5778,35 +5778,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5897,35 +5897,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6016,35 +6016,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6135,35 +6135,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6261,7 +6261,7 @@
         <v>3045</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3080</v>
+        <v>3085</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6507,7 +6507,7 @@
         <v>3053.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3192</v>
+        <v>3193</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9534,11 +9534,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>3080</v>
+        <v>3085</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,200원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,135원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.01695606925782262</v>
+        <v>0.01695606925782039</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>

--- a/argus/kship/models/187790_model.xlsx
+++ b/argus/kship/models/187790_model.xlsx
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5302,35 +5302,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5421,35 +5421,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5540,35 +5540,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5659,35 +5659,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5778,35 +5778,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5897,35 +5897,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6016,35 +6016,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6135,35 +6135,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10402,7 +10402,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/187790_model.xlsx
+++ b/argus/kship/models/187790_model.xlsx
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10402,7 +10402,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/187790_model.xlsx
+++ b/argus/kship/models/187790_model.xlsx
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
         <v>3045</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3085</v>
+        <v>2860</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6425,7 +6425,7 @@
         <v>2160</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>3010</v>
+        <v>2820</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6507,7 +6507,7 @@
         <v>3053.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3193</v>
+        <v>3137.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9534,7 +9534,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>3085</v>
+        <v>2860</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39003,7 +39003,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41238,7 +41238,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/187790_model.xlsx
+++ b/argus/kship/models/187790_model.xlsx
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5302,35 +5302,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5421,35 +5421,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5540,35 +5540,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5659,35 +5659,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5778,35 +5778,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5897,35 +5897,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6016,35 +6016,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6135,35 +6135,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6261,7 +6261,7 @@
         <v>3045</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2860</v>
+        <v>2775</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6425,7 +6425,7 @@
         <v>2160</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2820</v>
+        <v>2670</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6507,7 +6507,7 @@
         <v>3053.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3137.5</v>
+        <v>3092.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9534,11 +9534,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>2860</v>
+        <v>2775</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,135원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,080원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39003,7 +39003,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41238,7 +41238,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/187790_model.xlsx
+++ b/argus/kship/models/187790_model.xlsx
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5302,35 +5302,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5421,35 +5421,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5540,35 +5540,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5659,35 +5659,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5778,35 +5778,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5897,35 +5897,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6016,35 +6016,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6135,35 +6135,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6261,7 +6261,7 @@
         <v>3045</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2775</v>
+        <v>2680</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6425,7 +6425,7 @@
         <v>2160</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2670</v>
+        <v>2660</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6507,7 +6507,7 @@
         <v>3053.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3092.9</v>
+        <v>3049.4</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9534,11 +9534,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>2775</v>
+        <v>2680</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,080원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,850원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39003,7 +39003,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41238,7 +41238,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/187790_model.xlsx
+++ b/argus/kship/models/187790_model.xlsx
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5302,35 +5302,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5421,35 +5421,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5540,35 +5540,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5659,35 +5659,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5778,35 +5778,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5897,35 +5897,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6016,35 +6016,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6135,35 +6135,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6261,7 +6261,7 @@
         <v>3045</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2680</v>
+        <v>2565</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6425,7 +6425,7 @@
         <v>2160</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2660</v>
+        <v>2370</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6507,7 +6507,7 @@
         <v>3053.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3049.4</v>
+        <v>2915.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9534,11 +9534,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>2680</v>
+        <v>2565</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,850원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,490원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39003,7 +39003,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41238,7 +41238,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/187790_model.xlsx
+++ b/argus/kship/models/187790_model.xlsx
@@ -4424,7 +4424,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5302,35 +5302,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5421,35 +5421,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5540,35 +5540,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5659,35 +5659,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5778,35 +5778,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5897,35 +5897,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6016,35 +6016,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6135,35 +6135,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6261,7 +6261,7 @@
         <v>3045</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>2565</v>
+        <v>2300</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6425,7 +6425,7 @@
         <v>2160</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>2370</v>
+        <v>2225</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6507,7 +6507,7 @@
         <v>3053.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>2915.9</v>
+        <v>2754.1</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9534,11 +9534,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>2565</v>
+        <v>2300</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,490원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 2,405원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39003,7 +39003,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41238,7 +41238,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="33">
